--- a/港岛-坚尼地城及摩星岭-吉喆/吉喆_销控明细表.xlsx
+++ b/港岛-坚尼地城及摩星岭-吉喆/吉喆_销控明细表.xlsx
@@ -3146,7 +3146,7 @@
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         <v>10527000</v>
       </c>
       <c r="I55" s="5" t="n">
-        <v>27272</v>
+        <v>27343</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
@@ -9313,9 +9313,9 @@
       </c>
       <c r="C13" s="20" t="inlineStr">
         <is>
-          <t>B | 386呎 (1房)
+          <t>B | 385呎 (1房)
 $1053万
-$27,272/呎
+$27,343/呎
 (24年-07月-08日)</t>
         </is>
       </c>

--- a/港岛-坚尼地城及摩星岭-吉喆/吉喆_销控明细表.xlsx
+++ b/港岛-坚尼地城及摩星岭-吉喆/吉喆_销控明细表.xlsx
@@ -4526,7 +4526,7 @@
         </is>
       </c>
       <c r="E85" s="4" t="n">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>10239000</v>
       </c>
       <c r="I85" s="5" t="n">
-        <v>26526</v>
+        <v>26595</v>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
@@ -9574,9 +9574,9 @@
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>B | 386呎 (1房)
+          <t>B | 385呎 (1房)
 $1024万
-$26,526/呎
+$26,595/呎
 (25年-07月-20日)</t>
         </is>
       </c>

--- a/港岛-坚尼地城及摩星岭-吉喆/吉喆_销控明细表.xlsx
+++ b/港岛-坚尼地城及摩星岭-吉喆/吉喆_销控明细表.xlsx
@@ -3422,7 +3422,7 @@
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>6212000</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>21201</v>
+        <v>21129</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
@@ -9432,9 +9432,9 @@
       </c>
       <c r="G14" s="20" t="inlineStr">
         <is>
-          <t>F | 293呎 (开放式)
+          <t>F | 294呎 (开放式)
 $621万
-$21,201/呎
+$21,129/呎
 (24年-07月-10日)</t>
         </is>
       </c>

--- a/港岛-坚尼地城及摩星岭-吉喆/吉喆_销控明细表.xlsx
+++ b/港岛-坚尼地城及摩星岭-吉喆/吉喆_销控明细表.xlsx
@@ -1532,7 +1532,7 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
         <v>29800000</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>30470</v>
+        <v>30439</v>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
@@ -1716,7 +1716,7 @@
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
@@ -2962,7 +2962,7 @@
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>6258000</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>21286</v>
+        <v>21358</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         <v>10527000</v>
       </c>
       <c r="I55" s="5" t="n">
-        <v>27343</v>
+        <v>27272</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>6212000</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>21129</v>
+        <v>21201</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
@@ -4342,7 +4342,7 @@
         </is>
       </c>
       <c r="E81" s="4" t="n">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>6053000</v>
       </c>
       <c r="I81" s="5" t="n">
-        <v>20588</v>
+        <v>20659</v>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         </is>
       </c>
       <c r="E85" s="4" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>10239000</v>
       </c>
       <c r="I85" s="5" t="n">
-        <v>26595</v>
+        <v>26526</v>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         </is>
       </c>
       <c r="E115" s="4" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
@@ -5922,7 +5922,7 @@
         <v>10028000</v>
       </c>
       <c r="I115" s="5" t="n">
-        <v>26047</v>
+        <v>25979</v>
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
@@ -6182,7 +6182,7 @@
         </is>
       </c>
       <c r="E121" s="4" t="n">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F121" s="3" t="inlineStr">
         <is>
@@ -6198,7 +6198,7 @@
         <v>5875000</v>
       </c>
       <c r="I121" s="5" t="n">
-        <v>19983</v>
+        <v>20051</v>
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
@@ -6366,7 +6366,7 @@
         </is>
       </c>
       <c r="E125" s="4" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F125" s="3" t="inlineStr">
         <is>
@@ -6382,7 +6382,7 @@
         <v>9998000</v>
       </c>
       <c r="I125" s="5" t="n">
-        <v>25969</v>
+        <v>25902</v>
       </c>
       <c r="J125" s="3" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         </is>
       </c>
       <c r="E141" s="4" t="n">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
@@ -7118,7 +7118,7 @@
         <v>5786000</v>
       </c>
       <c r="I141" s="5" t="n">
-        <v>19680</v>
+        <v>19747</v>
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
         </is>
       </c>
       <c r="E145" s="4" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F145" s="3" t="inlineStr">
         <is>
@@ -7302,7 +7302,7 @@
         <v>9652000</v>
       </c>
       <c r="I145" s="5" t="n">
-        <v>25070</v>
+        <v>25005</v>
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
         </is>
       </c>
       <c r="E151" s="4" t="n">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F151" s="3" t="inlineStr">
         <is>
@@ -7578,7 +7578,7 @@
         <v>5751000</v>
       </c>
       <c r="I151" s="5" t="n">
-        <v>19561</v>
+        <v>19628</v>
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
@@ -7746,7 +7746,7 @@
         </is>
       </c>
       <c r="E155" s="4" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F155" s="3" t="inlineStr">
         <is>
@@ -7762,7 +7762,7 @@
         <v>9432000</v>
       </c>
       <c r="I155" s="5" t="n">
-        <v>24499</v>
+        <v>24435</v>
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
@@ -8206,7 +8206,7 @@
         </is>
       </c>
       <c r="E165" s="4" t="n">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F165" s="3" t="inlineStr">
         <is>
@@ -8222,7 +8222,7 @@
         <v>9391000</v>
       </c>
       <c r="I165" s="5" t="n">
-        <v>24392</v>
+        <v>24329</v>
       </c>
       <c r="J165" s="3" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         </is>
       </c>
       <c r="E170" s="4" t="n">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F170" s="3" t="inlineStr">
         <is>
@@ -8452,7 +8452,7 @@
         <v>5689000</v>
       </c>
       <c r="I170" s="5" t="n">
-        <v>19350</v>
+        <v>19416</v>
       </c>
       <c r="J170" s="3" t="inlineStr">
         <is>
@@ -9057,9 +9057,9 @@
       </c>
       <c r="D9" s="20" t="inlineStr">
         <is>
-          <t>C | 978呎 (3房)
+          <t>C | 979呎 (3房)
 $2980万
-$30,470/呎
+$30,439/呎
 (26年-01月-15日)</t>
         </is>
       </c>
@@ -9102,7 +9102,7 @@
       </c>
       <c r="D10" s="21" t="inlineStr">
         <is>
-          <t>C | 978呎 (3房)
+          <t>C | 979呎 (3房)
 -
 -
 (待售)</t>
@@ -9313,9 +9313,9 @@
       </c>
       <c r="C13" s="20" t="inlineStr">
         <is>
-          <t>B | 385呎 (1房)
+          <t>B | 386呎 (1房)
 $1053万
-$27,343/呎
+$27,272/呎
 (24年-07月-08日)</t>
         </is>
       </c>
@@ -9345,9 +9345,9 @@
       </c>
       <c r="G13" s="20" t="inlineStr">
         <is>
-          <t>F | 294呎 (开放式)
+          <t>F | 293呎 (开放式)
 $626万
-$21,286/呎
+$21,358/呎
 (24年-07月-07日)</t>
         </is>
       </c>
@@ -9432,9 +9432,9 @@
       </c>
       <c r="G14" s="20" t="inlineStr">
         <is>
-          <t>F | 294呎 (开放式)
+          <t>F | 293呎 (开放式)
 $621万
-$21,129/呎
+$21,201/呎
 (24年-07月-10日)</t>
         </is>
       </c>
@@ -9574,9 +9574,9 @@
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>B | 385呎 (1房)
+          <t>B | 386呎 (1房)
 $1024万
-$26,595/呎
+$26,526/呎
 (25年-07月-20日)</t>
         </is>
       </c>
@@ -9606,9 +9606,9 @@
       </c>
       <c r="G16" s="20" t="inlineStr">
         <is>
-          <t>F | 294呎 (开放式)
+          <t>F | 293呎 (开放式)
 $605万
-$20,588/呎
+$20,659/呎
 (24年-07月-08日)</t>
         </is>
       </c>
@@ -9835,9 +9835,9 @@
       </c>
       <c r="C19" s="20" t="inlineStr">
         <is>
-          <t>B | 385呎 (1房)
+          <t>B | 386呎 (1房)
 $1003万
-$26,047/呎
+$25,979/呎
 (25年-05月-22日)</t>
         </is>
       </c>
@@ -9922,9 +9922,9 @@
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>B | 385呎 (1房)
+          <t>B | 386呎 (1房)
 $1000万
-$25,969/呎
+$25,902/呎
 (25年-10月-21日)</t>
         </is>
       </c>
@@ -9954,9 +9954,9 @@
       </c>
       <c r="G20" s="20" t="inlineStr">
         <is>
-          <t>F | 294呎 (开放式)
+          <t>F | 293呎 (开放式)
 $588万
-$19,983/呎
+$20,051/呎
 (24年-07月-04日)</t>
         </is>
       </c>
@@ -10096,9 +10096,9 @@
       </c>
       <c r="C22" s="20" t="inlineStr">
         <is>
-          <t>B | 385呎 (1房)
+          <t>B | 386呎 (1房)
 $965万
-$25,070/呎
+$25,005/呎
 (25年-12月-07日)</t>
         </is>
       </c>
@@ -10128,9 +10128,9 @@
       </c>
       <c r="G22" s="20" t="inlineStr">
         <is>
-          <t>F | 294呎 (开放式)
+          <t>F | 293呎 (开放式)
 $579万
-$19,680/呎
+$19,747/呎
 (24年-09月-10日)</t>
         </is>
       </c>
@@ -10183,9 +10183,9 @@
       </c>
       <c r="C23" s="20" t="inlineStr">
         <is>
-          <t>B | 385呎 (1房)
+          <t>B | 386呎 (1房)
 $943万
-$24,499/呎
+$24,435/呎
 (25年-12月-10日)</t>
         </is>
       </c>
@@ -10215,9 +10215,9 @@
       </c>
       <c r="G23" s="20" t="inlineStr">
         <is>
-          <t>F | 294呎 (开放式)
+          <t>F | 293呎 (开放式)
 $575万
-$19,561/呎
+$19,628/呎
 (24年-09月-10日)</t>
         </is>
       </c>
@@ -10270,9 +10270,9 @@
       </c>
       <c r="C24" s="20" t="inlineStr">
         <is>
-          <t>B | 385呎 (1房)
+          <t>B | 386呎 (1房)
 $939万
-$24,392/呎
+$24,329/呎
 (25年-12月-11日)</t>
         </is>
       </c>
@@ -10389,9 +10389,9 @@
       </c>
       <c r="G25" s="20" t="inlineStr">
         <is>
-          <t>F | 294呎 (开放式)
+          <t>F | 293呎 (开放式)
 $569万
-$19,350/呎
+$19,416/呎
 (24年-07月-07日)</t>
         </is>
       </c>
